--- a/ttl_long/AdHoc_Net_0.xlsx
+++ b/ttl_long/AdHoc_Net_0.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,12 +443,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>80</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>42</t>
         </is>
       </c>
     </row>
@@ -465,7 +465,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>93</t>
         </is>
       </c>
     </row>
@@ -477,12 +477,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>468</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>1170</t>
         </is>
       </c>
     </row>
@@ -494,12 +494,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>98</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>198</t>
         </is>
       </c>
     </row>
@@ -511,12 +511,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>280</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>162</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>301</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>147</t>
         </is>
       </c>
     </row>
@@ -545,12 +545,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>346</t>
         </is>
       </c>
     </row>
@@ -562,12 +562,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>58</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>382</t>
         </is>
       </c>
     </row>
@@ -579,12 +579,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>308</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>317</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>409</t>
+          <t>445</t>
         </is>
       </c>
     </row>
@@ -613,12 +613,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>489</t>
+          <t>603</t>
         </is>
       </c>
     </row>
@@ -630,12 +630,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>284</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>449</t>
+          <t>524</t>
         </is>
       </c>
     </row>
@@ -647,12 +647,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>561</t>
         </is>
       </c>
     </row>
@@ -664,12 +664,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>225</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>553</t>
+          <t>603</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>295</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>629</t>
         </is>
       </c>
     </row>
@@ -698,12 +698,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>838</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>54</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>929</t>
         </is>
       </c>
     </row>
@@ -732,12 +732,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>363</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>714</t>
+          <t>775</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>74</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>916</t>
+          <t>968</t>
         </is>
       </c>
     </row>
@@ -766,12 +766,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>108</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>910</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>354</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>844</t>
+          <t>957</t>
         </is>
       </c>
     </row>
@@ -800,12 +800,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>48</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1091</t>
+          <t>1157</t>
         </is>
       </c>
     </row>
@@ -817,12 +817,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>242</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>1142</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>336</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1041</t>
+          <t>1129</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>107</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1180</t>
+          <t>1295</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>107</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1095</t>
+          <t>1243</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>280</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1185</t>
+          <t>1306</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1450</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>197</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>1526</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>657</t>
         </is>
       </c>
     </row>
@@ -953,80 +953,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>311</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1482</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>1495</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>296</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>1429</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>1618</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>1522</t>
+          <t>979</t>
         </is>
       </c>
     </row>
@@ -1041,7 +973,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D90"/>
+  <dimension ref="A1:D80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1096,7 +1028,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1118,7 +1050,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1140,7 +1072,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1206,7 +1138,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1228,7 +1160,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1250,7 +1182,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1272,7 +1204,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1289,12 +1221,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1316,7 +1248,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1338,7 +1270,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1382,7 +1314,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1399,7 +1331,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1421,12 +1353,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1443,7 +1375,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1465,12 +1397,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1492,7 +1424,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1509,12 +1441,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1531,7 +1463,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1558,7 +1490,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1575,12 +1507,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1602,7 +1534,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1619,12 +1551,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1646,7 +1578,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1668,7 +1600,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1685,12 +1617,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1712,7 +1644,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1734,7 +1666,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1795,12 +1727,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1817,12 +1749,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1839,12 +1771,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1861,12 +1793,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1883,7 +1815,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1905,12 +1837,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1927,12 +1859,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1949,12 +1881,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1971,12 +1903,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1993,12 +1925,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2015,12 +1947,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2037,12 +1969,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2059,12 +1991,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2081,12 +2013,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2103,12 +2035,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2125,12 +2057,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2147,12 +2079,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2169,12 +2101,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2196,7 +2128,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2213,12 +2145,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2235,12 +2167,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2257,12 +2189,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2279,12 +2211,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2301,12 +2233,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2323,12 +2255,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2345,12 +2277,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2367,12 +2299,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2389,12 +2321,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2416,7 +2348,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2433,12 +2365,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
           <t>22</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>25</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2455,12 +2387,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2482,7 +2414,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2499,12 +2431,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2543,12 +2475,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2565,12 +2497,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2587,12 +2519,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2609,7 +2541,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2636,7 +2568,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2653,12 +2585,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2680,7 +2612,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2702,7 +2634,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2719,12 +2651,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2741,12 +2673,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2768,7 +2700,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2785,12 +2717,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2799,226 +2731,6 @@
         </is>
       </c>
       <c r="D80" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
@@ -3057,7 +2769,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -3067,7 +2779,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
@@ -3093,7 +2805,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>jamm_powe</t>
+          <t>jamm_power</t>
         </is>
       </c>
       <c r="B6" t="n">

--- a/ttl_long/AdHoc_Net_0.xlsx
+++ b/ttl_long/AdHoc_Net_0.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,12 +443,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -460,12 +460,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>209</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -477,12 +477,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>307</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1170</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -494,12 +494,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>69</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>66</t>
         </is>
       </c>
     </row>
@@ -511,12 +511,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>198</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>58</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>347</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>116</t>
         </is>
       </c>
     </row>
@@ -545,12 +545,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>188</t>
         </is>
       </c>
     </row>
@@ -562,12 +562,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>141</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>212</t>
         </is>
       </c>
     </row>
@@ -579,12 +579,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>299</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>224</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>445</t>
+          <t>449</t>
         </is>
       </c>
     </row>
@@ -613,12 +613,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>109</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>294</t>
         </is>
       </c>
     </row>
@@ -630,12 +630,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>345</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>407</t>
         </is>
       </c>
     </row>
@@ -647,12 +647,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>114</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>425</t>
         </is>
       </c>
     </row>
@@ -664,12 +664,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>167</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>489</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>306</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>474</t>
         </is>
       </c>
     </row>
@@ -698,12 +698,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>838</t>
+          <t>640</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>254</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>666</t>
         </is>
       </c>
     </row>
@@ -732,12 +732,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>311</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>775</t>
+          <t>596</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>101</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>771</t>
         </is>
       </c>
     </row>
@@ -766,12 +766,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>219</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>816</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>277</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>784</t>
         </is>
       </c>
     </row>
@@ -800,12 +800,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>49</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1157</t>
+          <t>937</t>
         </is>
       </c>
     </row>
@@ -817,12 +817,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>217</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1142</t>
+          <t>855</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>350</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>885</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>85</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>965</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>145</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1243</t>
+          <t>1041</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>305</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>964</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>77</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1450</t>
+          <t>1094</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>177</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1526</t>
+          <t>1205</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>279</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>1127</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,182 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>979</t>
+          <t>1228</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1284</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1375</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1308</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1348</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1525</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1449</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>292</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1453</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>366</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1008</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1625</t>
         </is>
       </c>
     </row>
@@ -973,7 +1143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D80"/>
+  <dimension ref="A1:D116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1006,7 +1176,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1028,7 +1198,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1050,7 +1220,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1072,7 +1242,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1094,7 +1264,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1116,7 +1286,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1160,7 +1330,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1182,7 +1352,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1204,7 +1374,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1226,7 +1396,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1248,7 +1418,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1270,7 +1440,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1287,12 +1457,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1314,7 +1484,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1331,12 +1501,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1353,12 +1523,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1375,12 +1545,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1402,7 +1572,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1424,7 +1594,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1441,7 +1611,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1468,7 +1638,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1490,7 +1660,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1507,12 +1677,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1534,7 +1704,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1551,12 +1721,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1573,12 +1743,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1595,12 +1765,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1617,12 +1787,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1639,12 +1809,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1661,12 +1831,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1683,12 +1853,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1705,12 +1875,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1727,12 +1897,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1749,12 +1919,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1771,12 +1941,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1793,7 +1963,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1815,12 +1985,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1837,12 +2007,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1859,12 +2029,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1881,12 +2051,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
           <t>15</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>29</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1903,12 +2073,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1925,12 +2095,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1947,12 +2117,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1969,12 +2139,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1996,7 +2166,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2018,7 +2188,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2035,7 +2205,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2062,7 +2232,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2079,12 +2249,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2101,12 +2271,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2128,7 +2298,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2145,12 +2315,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2167,12 +2337,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2189,7 +2359,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2211,12 +2381,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2233,12 +2403,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2255,12 +2425,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2277,12 +2447,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2299,12 +2469,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2321,12 +2491,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2343,12 +2513,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2365,12 +2535,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2387,12 +2557,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2409,12 +2579,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2431,12 +2601,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2453,12 +2623,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2475,12 +2645,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2497,12 +2667,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2519,12 +2689,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2541,12 +2711,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2563,12 +2733,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2585,7 +2755,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2607,12 +2777,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2629,12 +2799,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2651,12 +2821,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2673,12 +2843,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
           <t>29</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2695,12 +2865,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2717,20 +2887,812 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
@@ -2779,7 +3741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4">
@@ -2799,7 +3761,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>800</v>
+        <v>250</v>
       </c>
     </row>
     <row r="6">

--- a/ttl_long/AdHoc_Net_0.xlsx
+++ b/ttl_long/AdHoc_Net_0.xlsx
@@ -443,12 +443,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>106</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>44</t>
         </is>
       </c>
     </row>
@@ -460,12 +460,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>146</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>75</t>
         </is>
       </c>
     </row>
@@ -477,7 +477,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>384</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -494,12 +494,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>180</t>
         </is>
       </c>
     </row>
@@ -511,12 +511,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>168</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>49</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>340</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>136</t>
         </is>
       </c>
     </row>
@@ -545,12 +545,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>83</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>246</t>
         </is>
       </c>
     </row>
@@ -562,12 +562,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>238</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>207</t>
         </is>
       </c>
     </row>
@@ -579,12 +579,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>365</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>289</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>74</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>449</t>
+          <t>434</t>
         </is>
       </c>
     </row>
@@ -613,12 +613,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>254</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>343</t>
         </is>
       </c>
     </row>
@@ -630,12 +630,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>317</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>383</t>
         </is>
       </c>
     </row>
@@ -647,12 +647,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>464</t>
         </is>
       </c>
     </row>
@@ -664,12 +664,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>115</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>489</t>
+          <t>496</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>282</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>539</t>
         </is>
       </c>
     </row>
@@ -703,7 +703,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>677</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>56</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>613</t>
         </is>
       </c>
     </row>
@@ -732,12 +732,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>312</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>636</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>69</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>766</t>
         </is>
       </c>
     </row>
@@ -766,12 +766,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>120</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>816</t>
+          <t>677</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>361</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>788</t>
         </is>
       </c>
     </row>
@@ -800,12 +800,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>937</t>
+          <t>849</t>
         </is>
       </c>
     </row>
@@ -817,12 +817,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>218</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>855</t>
+          <t>932</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>297</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>874</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>116</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>965</t>
+          <t>1004</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>150</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1041</t>
+          <t>1002</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>390</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>994</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>58</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1094</t>
+          <t>1183</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>103</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1205</t>
+          <t>1171</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>383</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>1147</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1228</t>
+          <t>1230</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>246</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1284</t>
+          <t>1258</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>299</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1202</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>66</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1375</t>
+          <t>1342</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>226</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>1379</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>365</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1348</t>
+          <t>1390</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>57</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1525</t>
+          <t>1412</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>1467</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>292</t>
+          <t>369</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1453</t>
+          <t>1475</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>1560</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>87</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1625</t>
+          <t>1634</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D116"/>
+  <dimension ref="A1:D115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1325,7 +1325,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1391,7 +1391,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1523,12 +1523,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1897,12 +1897,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1919,12 +1919,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1968,7 +1968,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1985,7 +1985,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2051,12 +2051,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2095,12 +2095,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2139,12 +2139,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2161,12 +2161,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2183,7 +2183,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2205,12 +2205,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2227,12 +2227,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2249,12 +2249,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2293,12 +2293,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2315,12 +2315,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2337,12 +2337,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2381,12 +2381,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2403,12 +2403,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2425,12 +2425,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2469,12 +2469,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2491,12 +2491,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2535,12 +2535,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2557,12 +2557,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2601,12 +2601,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2623,12 +2623,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2667,12 +2667,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2689,12 +2689,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
           <t>23</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>22</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2733,12 +2733,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2755,12 +2755,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2777,12 +2777,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2799,12 +2799,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2821,7 +2821,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2865,12 +2865,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2909,12 +2909,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2931,12 +2931,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2997,12 +2997,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3063,12 +3063,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3090,7 +3090,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3129,12 +3129,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3195,12 +3195,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
           <t>31</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>34</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3217,12 +3217,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3239,12 +3239,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3261,12 +3261,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3349,12 +3349,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3393,12 +3393,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3415,12 +3415,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3459,12 +3459,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3481,12 +3481,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3525,7 +3525,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3547,12 +3547,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3591,7 +3591,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3613,12 +3613,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3635,12 +3635,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3671,28 +3671,6 @@
         </is>
       </c>
       <c r="D115" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
@@ -3741,7 +3719,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4">
